--- a/main/ig/ValueSet-fr-vs-encounter-class.xlsx
+++ b/main/ig/ValueSet-fr-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-encounter-class.xlsx
+++ b/main/ig/ValueSet-fr-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-encounter-class.xlsx
+++ b/main/ig/ValueSet-fr-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-encounter-class.xlsx
+++ b/main/ig/ValueSet-fr-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-encounter-class.xlsx
+++ b/main/ig/ValueSet-fr-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-encounter-class.xlsx
+++ b/main/ig/ValueSet-fr-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-encounter-class.xlsx
+++ b/main/ig/ValueSet-fr-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-encounter-class.xlsx
+++ b/main/ig/ValueSet-fr-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
